--- a/public/exports-60-250-with-coowners/29189781.xlsx
+++ b/public/exports-60-250-with-coowners/29189781.xlsx
@@ -5014,7 +5014,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089559</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089560</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089560</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
